--- a/source/bin/excel/mmo.xlsx
+++ b/source/bin/excel/mmo.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A120B6AB-DCF4-4D7C-93EE-FB9AC24EA398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F5BD99-04CF-40A5-9B9A-5BFBDE445636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="641" firstSheet="2" activeTab="5" xr2:uid="{48F72880-0361-4713-AC36-DD070408E0C2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="641" activeTab="3" xr2:uid="{48F72880-0361-4713-AC36-DD070408E0C2}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="8" r:id="rId1"/>
     <sheet name="mmo_activity" sheetId="1" r:id="rId2"/>
     <sheet name="mmo_character" sheetId="2" r:id="rId3"/>
-    <sheet name="mmo_level" sheetId="6" r:id="rId4"/>
-    <sheet name="mmo_enemy" sheetId="3" r:id="rId5"/>
-    <sheet name="mmo_equipment" sheetId="4" r:id="rId6"/>
-    <sheet name="mmo_equipment_buff" sheetId="5" r:id="rId7"/>
+    <sheet name="mmo_npc" sheetId="9" r:id="rId4"/>
+    <sheet name="mmo_level" sheetId="6" r:id="rId5"/>
+    <sheet name="mmo_enemy" sheetId="3" r:id="rId6"/>
+    <sheet name="mmo_equipment" sheetId="4" r:id="rId7"/>
+    <sheet name="mmo_equipment_buff" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -219,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="413">
   <si>
     <t>##</t>
   </si>
@@ -1102,30 +1103,390 @@
     <t>wq_4_mofazhang</t>
   </si>
   <si>
+    <t>res_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spine名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>warrior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头1-王冠-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头1-王冠-5星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头1-王冠-4星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头1-王冠-3星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头1-王冠-2星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头2-王冠-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头2-王冠-2星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头2-王冠-3星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头2-王冠-4星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头2-王冠-5星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头3-帽子-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头3-帽子-2星</t>
+  </si>
+  <si>
+    <t>头3-帽子-3星</t>
+  </si>
+  <si>
+    <t>头3-帽子-4星</t>
+  </si>
+  <si>
+    <t>头3-帽子-5星</t>
+  </si>
+  <si>
+    <t>头4-帽子-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头4-帽子-2星</t>
+  </si>
+  <si>
+    <t>头4-帽子-3星</t>
+  </si>
+  <si>
+    <t>头4-帽子-4星</t>
+  </si>
+  <si>
+    <t>头4-帽子-5星</t>
+  </si>
+  <si>
+    <t>头5-眼罩-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头5-眼罩-2星</t>
+  </si>
+  <si>
+    <t>头5-眼罩-3星</t>
+  </si>
+  <si>
+    <t>头5-眼罩-4星</t>
+  </si>
+  <si>
+    <t>头5-眼罩-5星</t>
+  </si>
+  <si>
+    <t>头6-眼罩-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头6-眼罩-2星</t>
+  </si>
+  <si>
+    <t>头6-眼罩-3星</t>
+  </si>
+  <si>
+    <t>头6-眼罩-4星</t>
+  </si>
+  <si>
+    <t>头6-眼罩-5星</t>
+  </si>
+  <si>
+    <t>头7-眼罩-5星</t>
+  </si>
+  <si>
+    <t>头7-眼罩-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头7-眼罩-2星</t>
+  </si>
+  <si>
+    <t>头7-眼罩-3星</t>
+  </si>
+  <si>
+    <t>头7-眼罩-4星</t>
+  </si>
+  <si>
+    <t>防1-蓝-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防1-蓝-2星</t>
+  </si>
+  <si>
+    <t>防1-蓝-3星</t>
+  </si>
+  <si>
+    <t>防1-蓝-4星</t>
+  </si>
+  <si>
+    <t>防1-蓝-5星</t>
+  </si>
+  <si>
+    <t>防2-蓝-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防2-蓝-2星</t>
+  </si>
+  <si>
+    <t>防2-蓝-3星</t>
+  </si>
+  <si>
+    <t>防2-蓝-4星</t>
+  </si>
+  <si>
+    <t>防2-蓝-5星</t>
+  </si>
+  <si>
+    <t>防3-红-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防3-红-2星</t>
+  </si>
+  <si>
+    <t>防3-红-3星</t>
+  </si>
+  <si>
+    <t>防3-红-4星</t>
+  </si>
+  <si>
+    <t>防3-红-5星</t>
+  </si>
+  <si>
+    <t>防4-红-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防4-红-2星</t>
+  </si>
+  <si>
+    <t>防4-红-3星</t>
+  </si>
+  <si>
+    <t>防4-红-4星</t>
+  </si>
+  <si>
+    <t>防4-红-5星</t>
+  </si>
+  <si>
+    <t>防6-紫-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防5-紫-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防5-紫-2星</t>
+  </si>
+  <si>
+    <t>防5-紫-3星</t>
+  </si>
+  <si>
+    <t>防5-紫-4星</t>
+  </si>
+  <si>
+    <t>防5-紫-5星</t>
+  </si>
+  <si>
+    <t>防6-紫-2星</t>
+  </si>
+  <si>
+    <t>防6-紫-3星</t>
+  </si>
+  <si>
+    <t>防6-紫-4星</t>
+  </si>
+  <si>
+    <t>防6-紫-5星</t>
+  </si>
+  <si>
+    <t>防7-紫-1星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防7-紫-2星</t>
+  </si>
+  <si>
+    <t>防7-紫-3星</t>
+  </si>
+  <si>
+    <t>防7-紫-4星</t>
+  </si>
+  <si>
+    <t>防7-紫-5星</t>
+  </si>
+  <si>
+    <t>对应function_item表的道具id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equipment_buff_desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备效果描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>wq_5_mofazhang</t>
-  </si>
-  <si>
-    <t>80000001,80000049,80000085</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80000017,80000049,80000085</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80000033,80000049,80000085</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>res_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spine名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toushi_0_1</t>
+  </si>
+  <si>
+    <t>toushi_1_wangguan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toushi_2_wangguan</t>
+  </si>
+  <si>
+    <t>toushi_3_wangguan</t>
+  </si>
+  <si>
+    <t>toushi_4_wangguan</t>
+  </si>
+  <si>
+    <t>toushi_5_wangguan</t>
+  </si>
+  <si>
+    <t>toushi_1_maozi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toushi_2_maozi</t>
+  </si>
+  <si>
+    <t>toushi_3_maozi</t>
+  </si>
+  <si>
+    <t>toushi_4_maozi</t>
+  </si>
+  <si>
+    <t>toushi_5_maozi</t>
+  </si>
+  <si>
+    <t>toushi_1_yanzhao</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>toushi_2_yanzhao</t>
+  </si>
+  <si>
+    <t>toushi_3_yanzhao</t>
+  </si>
+  <si>
+    <t>toushi_4_yanzhao</t>
+  </si>
+  <si>
+    <t>toushi_5_yanzhao</t>
+  </si>
+  <si>
+    <t>toushi_5_yanzhao</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yifu_0_hui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yifu_1_lan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yifu_2_lan</t>
+  </si>
+  <si>
+    <t>yifu_3_lan</t>
+  </si>
+  <si>
+    <t>yifu_4_lan</t>
+  </si>
+  <si>
+    <t>yifu_5_lan</t>
+  </si>
+  <si>
+    <t>yifu_1_red</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yifu_2_red</t>
+  </si>
+  <si>
+    <t>yifu_3_red</t>
+  </si>
+  <si>
+    <t>yifu_4_red</t>
+  </si>
+  <si>
+    <t>yifu_5_red</t>
+  </si>
+  <si>
+    <t>yifu_1_zi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yifu_2_zi</t>
+  </si>
+  <si>
+    <t>yifu_3_zi</t>
+  </si>
+  <si>
+    <t>yifu_4_zi</t>
+  </si>
+  <si>
+    <t>yifu_5_zi</t>
+  </si>
+  <si>
+    <t>yifu_5_zi</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1133,374 +1494,201 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>warrior</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头1-王冠-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头1-王冠-5星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头1-王冠-4星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头1-王冠-3星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头1-王冠-2星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头2-王冠-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头2-王冠-2星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头2-王冠-3星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头2-王冠-4星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头2-王冠-5星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头3-帽子-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头3-帽子-2星</t>
-  </si>
-  <si>
-    <t>头3-帽子-3星</t>
-  </si>
-  <si>
-    <t>头3-帽子-4星</t>
-  </si>
-  <si>
-    <t>头3-帽子-5星</t>
-  </si>
-  <si>
-    <t>头4-帽子-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头4-帽子-2星</t>
-  </si>
-  <si>
-    <t>头4-帽子-3星</t>
-  </si>
-  <si>
-    <t>头4-帽子-4星</t>
-  </si>
-  <si>
-    <t>头4-帽子-5星</t>
-  </si>
-  <si>
-    <t>头5-眼罩-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头5-眼罩-2星</t>
-  </si>
-  <si>
-    <t>头5-眼罩-3星</t>
-  </si>
-  <si>
-    <t>头5-眼罩-4星</t>
-  </si>
-  <si>
-    <t>头5-眼罩-5星</t>
-  </si>
-  <si>
-    <t>头6-眼罩-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头6-眼罩-2星</t>
-  </si>
-  <si>
-    <t>头6-眼罩-3星</t>
-  </si>
-  <si>
-    <t>头6-眼罩-4星</t>
-  </si>
-  <si>
-    <t>头6-眼罩-5星</t>
-  </si>
-  <si>
-    <t>头7-眼罩-5星</t>
-  </si>
-  <si>
-    <t>头7-眼罩-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头7-眼罩-2星</t>
-  </si>
-  <si>
-    <t>头7-眼罩-3星</t>
-  </si>
-  <si>
-    <t>头7-眼罩-4星</t>
-  </si>
-  <si>
-    <t>防1-蓝-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防1-蓝-2星</t>
-  </si>
-  <si>
-    <t>防1-蓝-3星</t>
-  </si>
-  <si>
-    <t>防1-蓝-4星</t>
-  </si>
-  <si>
-    <t>防1-蓝-5星</t>
-  </si>
-  <si>
-    <t>防2-蓝-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防2-蓝-2星</t>
-  </si>
-  <si>
-    <t>防2-蓝-3星</t>
-  </si>
-  <si>
-    <t>防2-蓝-4星</t>
-  </si>
-  <si>
-    <t>防2-蓝-5星</t>
-  </si>
-  <si>
-    <t>防3-红-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防3-红-2星</t>
-  </si>
-  <si>
-    <t>防3-红-3星</t>
-  </si>
-  <si>
-    <t>防3-红-4星</t>
-  </si>
-  <si>
-    <t>防3-红-5星</t>
-  </si>
-  <si>
-    <t>防4-红-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防4-红-2星</t>
-  </si>
-  <si>
-    <t>防4-红-3星</t>
-  </si>
-  <si>
-    <t>防4-红-4星</t>
-  </si>
-  <si>
-    <t>防4-红-5星</t>
-  </si>
-  <si>
-    <t>防6-紫-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防5-紫-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防5-紫-2星</t>
-  </si>
-  <si>
-    <t>防5-紫-3星</t>
-  </si>
-  <si>
-    <t>防5-紫-4星</t>
-  </si>
-  <si>
-    <t>防5-紫-5星</t>
-  </si>
-  <si>
-    <t>防6-紫-2星</t>
-  </si>
-  <si>
-    <t>防6-紫-3星</t>
-  </si>
-  <si>
-    <t>防6-紫-4星</t>
-  </si>
-  <si>
-    <t>防6-紫-5星</t>
-  </si>
-  <si>
-    <t>防7-紫-1星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防7-紫-2星</t>
-  </si>
-  <si>
-    <t>防7-紫-3星</t>
-  </si>
-  <si>
-    <t>防7-紫-4星</t>
-  </si>
-  <si>
-    <t>防7-紫-5星</t>
-  </si>
-  <si>
-    <t>对应function_item表的道具id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>equipment_buff_desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备效果描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wq_5_mofazhang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>toushi_0_1</t>
-  </si>
-  <si>
-    <t>toushi_1_wangguan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>toushi_2_wangguan</t>
-  </si>
-  <si>
-    <t>toushi_3_wangguan</t>
-  </si>
-  <si>
-    <t>toushi_4_wangguan</t>
-  </si>
-  <si>
-    <t>toushi_5_wangguan</t>
-  </si>
-  <si>
-    <t>toushi_1_maozi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>toushi_2_maozi</t>
-  </si>
-  <si>
-    <t>toushi_3_maozi</t>
-  </si>
-  <si>
-    <t>toushi_4_maozi</t>
-  </si>
-  <si>
-    <t>toushi_5_maozi</t>
-  </si>
-  <si>
-    <t>toushi_1_yanzhao</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>toushi_2_yanzhao</t>
-  </si>
-  <si>
-    <t>toushi_3_yanzhao</t>
-  </si>
-  <si>
-    <t>toushi_4_yanzhao</t>
-  </si>
-  <si>
-    <t>toushi_5_yanzhao</t>
-  </si>
-  <si>
-    <t>toushi_5_yanzhao</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yifu_0_hui</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yifu_1_lan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yifu_2_lan</t>
-  </si>
-  <si>
-    <t>yifu_3_lan</t>
-  </si>
-  <si>
-    <t>yifu_4_lan</t>
-  </si>
-  <si>
-    <t>yifu_5_lan</t>
-  </si>
-  <si>
-    <t>yifu_1_red</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yifu_2_red</t>
-  </si>
-  <si>
-    <t>yifu_3_red</t>
-  </si>
-  <si>
-    <t>yifu_4_red</t>
-  </si>
-  <si>
-    <t>yifu_5_red</t>
-  </si>
-  <si>
-    <t>yifu_1_zi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yifu_2_zi</t>
-  </si>
-  <si>
-    <t>yifu_3_zi</t>
-  </si>
-  <si>
-    <t>yifu_4_zi</t>
-  </si>
-  <si>
-    <t>yifu_5_zi</t>
-  </si>
-  <si>
-    <t>yifu_5_zi</t>
+    <t>70001100,70001148,70001184</t>
+  </si>
+  <si>
+    <t>70001116,70001148,70001184</t>
+  </si>
+  <si>
+    <t>70001132,70001148,70001184</t>
+  </si>
+  <si>
+    <t>mmonpc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mmo_npc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑士npc1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战士npc1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法师npc1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑士npc2号</t>
+  </si>
+  <si>
+    <t>剑士npc3号</t>
+  </si>
+  <si>
+    <t>战士npc2号</t>
+  </si>
+  <si>
+    <t>战士npc3号</t>
+  </si>
+  <si>
+    <t>法师npc2号</t>
+  </si>
+  <si>
+    <t>法师npc3号</t>
+  </si>
+  <si>
+    <t>npcid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001101,70001149,70001185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001106,70001159,70001195</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001111,70001169,70001205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001117,70001149,70001185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001133,70001149,70001185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001122,70001159,70001195</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001138,70001159,70001195</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001127,70001169,70001185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001143,70001169,70001185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>职业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accessible_days</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机时段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001102,70001150,70001186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001107,70001160,70001196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001112,70001170,70001206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001118,70001150,70001186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001123,70001160,70001196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001128,70001170,70001186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001134,70001150,70001186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001139,70001160,70001196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001144,70001170,70001186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001103,70001151,70001187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001108,70001161,70001197</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001113,70001171,70001207</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001119,70001151,70001187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001124,70001161,70001197</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001129,70001171,70001187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001135,70001151,70001187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001140,70001161,70001197</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70001145,70001171,70001187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前活动时间最长持续30天，如果需要更长的持续时间需要联系开发修改角色缓存过期时间</t>
+  </si>
+  <si>
+    <t>npc_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc名称,str/event</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1592,7 +1780,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1616,6 +1804,36 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1932,7 +2150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D443A4F4-E68A-4E6D-A594-946853DC91DD}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.375" bestFit="1" customWidth="1"/>
@@ -1941,7 +2159,7 @@
     <col min="5" max="5" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -1958,7 +2176,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1971,8 +2189,11 @@
       <c r="E2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -1986,7 +2207,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -2000,7 +2221,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -2014,7 +2235,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -2028,7 +2249,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -2040,6 +2261,20 @@
       </c>
       <c r="E7" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>364</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -2199,7 +2434,7 @@
         <v>201</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -2243,7 +2478,7 @@
         <v>203</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -2287,7 +2522,7 @@
         <v>14</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -2301,7 +2536,7 @@
         <v>166</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -2336,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>245</v>
+        <v>360</v>
       </c>
       <c r="L5" s="3">
         <v>26040001</v>
@@ -2345,7 +2580,7 @@
         <v>26040004</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -2380,7 +2615,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>246</v>
+        <v>361</v>
       </c>
       <c r="L6" s="3">
         <v>26040002</v>
@@ -2389,7 +2624,7 @@
         <v>26040005</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -2424,7 +2659,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>247</v>
+        <v>362</v>
       </c>
       <c r="L7" s="3">
         <v>26040003</v>
@@ -2433,7 +2668,7 @@
         <v>26040006</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -2444,6 +2679,741 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290880EC-C591-483F-99ED-0FF1550DB29B}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.75" style="16" customWidth="1"/>
+    <col min="2" max="2" width="9" style="16"/>
+    <col min="3" max="3" width="11.375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="16" customWidth="1"/>
+    <col min="5" max="5" width="30" style="13" customWidth="1"/>
+    <col min="6" max="6" width="36.25" style="16" customWidth="1"/>
+    <col min="7" max="7" width="17.125" style="16" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="G4" s="12" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1001</v>
+      </c>
+      <c r="D5" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G5" s="12">
+        <v>26041001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B6" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1002</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G6" s="12">
+        <v>26041001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B7" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C7" s="12">
+        <v>1003</v>
+      </c>
+      <c r="D7" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G7" s="12">
+        <v>26041001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B8" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C8" s="12">
+        <v>1004</v>
+      </c>
+      <c r="D8" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G8" s="12">
+        <v>26041002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B9" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C9" s="12">
+        <v>1005</v>
+      </c>
+      <c r="D9" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G9" s="12">
+        <v>26041002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B10" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C10" s="12">
+        <v>1006</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G10" s="12">
+        <v>26041002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="B11" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C11" s="12">
+        <v>1007</v>
+      </c>
+      <c r="D11" s="12">
+        <v>1003</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G11" s="12">
+        <v>26041003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="B12" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1008</v>
+      </c>
+      <c r="D12" s="12">
+        <v>1003</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G12" s="12">
+        <v>26041003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="B13" s="18">
+        <v>260401</v>
+      </c>
+      <c r="C13" s="18">
+        <v>1009</v>
+      </c>
+      <c r="D13" s="18">
+        <v>1003</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="G13" s="18">
+        <v>26041003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B14" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1001</v>
+      </c>
+      <c r="D14" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G14" s="12">
+        <v>26041004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B15" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1002</v>
+      </c>
+      <c r="D15" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G15" s="12">
+        <v>26041004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B16" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1003</v>
+      </c>
+      <c r="D16" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G16" s="12">
+        <v>26041004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B17" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C17" s="12">
+        <v>1004</v>
+      </c>
+      <c r="D17" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G17" s="12">
+        <v>26041005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B18" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1005</v>
+      </c>
+      <c r="D18" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G18" s="12">
+        <v>26041005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B19" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1006</v>
+      </c>
+      <c r="D19" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G19" s="12">
+        <v>26041005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="B20" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1007</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1003</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G20" s="12">
+        <v>26041006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="B21" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C21" s="12">
+        <v>1008</v>
+      </c>
+      <c r="D21" s="12">
+        <v>1003</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G21" s="12">
+        <v>26041006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B22" s="6">
+        <v>260401</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1009</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1003</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="G22" s="6">
+        <v>26041006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B23" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C23" s="12">
+        <v>1001</v>
+      </c>
+      <c r="D23" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G23" s="12">
+        <v>26041007</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B24" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C24" s="12">
+        <v>1002</v>
+      </c>
+      <c r="D24" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G24" s="12">
+        <v>26041007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B25" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C25" s="12">
+        <v>1003</v>
+      </c>
+      <c r="D25" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G25" s="12">
+        <v>26041007</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B26" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C26" s="12">
+        <v>1004</v>
+      </c>
+      <c r="D26" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G26" s="12">
+        <v>26041008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B27" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C27" s="12">
+        <v>1005</v>
+      </c>
+      <c r="D27" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G27" s="12">
+        <v>26041008</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B28" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C28" s="12">
+        <v>1006</v>
+      </c>
+      <c r="D28" s="12">
+        <v>1002</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G28" s="12">
+        <v>26041008</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C29" s="12">
+        <v>1007</v>
+      </c>
+      <c r="D29" s="12">
+        <v>1003</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G29" s="12">
+        <v>26041009</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="B30" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C30" s="12">
+        <v>1008</v>
+      </c>
+      <c r="D30" s="12">
+        <v>1003</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G30" s="12">
+        <v>26041009</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="B31" s="12">
+        <v>260401</v>
+      </c>
+      <c r="C31" s="12">
+        <v>1009</v>
+      </c>
+      <c r="D31" s="12">
+        <v>1003</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G31" s="12">
+        <v>26041009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F32" s="13"/>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E33" s="12"/>
+      <c r="F33" s="13"/>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E34" s="12"/>
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E35" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5544121B-8F71-43ED-A177-024D7F83210C}">
   <dimension ref="A1:K104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -5781,7 +6751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E28B2205-5D9A-40F5-9B3C-9ED4E9833394}">
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -5830,7 +6800,7 @@
         <v>35</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -5865,7 +6835,7 @@
         <v>36</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -5900,7 +6870,7 @@
         <v>30</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -5908,7 +6878,7 @@
         <v>4</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>251</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -6437,7 +7407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCC59E2-147A-4888-B3BB-8FC31EA0553D}">
   <dimension ref="A1:Q124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6519,7 +7489,7 @@
         <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>95</v>
@@ -6619,7 +7589,7 @@
         <v>166</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -7056,7 +8026,7 @@
         <v>100</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
@@ -7085,7 +8055,7 @@
         <v>200</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
@@ -7114,7 +8084,7 @@
         <v>400</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
@@ -7143,7 +8113,7 @@
         <v>800</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
@@ -7172,7 +8142,7 @@
         <v>1600</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
@@ -7201,7 +8171,7 @@
         <v>3200</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
@@ -7230,7 +8200,7 @@
         <v>200</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
@@ -7259,7 +8229,7 @@
         <v>400</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
@@ -7288,7 +8258,7 @@
         <v>800</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
@@ -7317,7 +8287,7 @@
         <v>1600</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
@@ -7346,7 +8316,7 @@
         <v>3200</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
@@ -7375,7 +8345,7 @@
         <v>200</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
@@ -7404,7 +8374,7 @@
         <v>400</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
@@ -7433,7 +8403,7 @@
         <v>800</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
@@ -7462,7 +8432,7 @@
         <v>1600</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -7491,7 +8461,7 @@
         <v>3200</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="Q36" s="3"/>
     </row>
@@ -7935,7 +8905,7 @@
         <v>3200</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="Q52" s="3"/>
     </row>
@@ -7959,12 +8929,12 @@
         <v>100</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B54" s="3">
         <v>260401</v>
@@ -7985,12 +8955,12 @@
         <v>200</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B55" s="3">
         <v>260401</v>
@@ -8011,12 +8981,12 @@
         <v>400</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B56" s="3">
         <v>260401</v>
@@ -8037,12 +9007,12 @@
         <v>800</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B57" s="3">
         <v>260401</v>
@@ -8063,12 +9033,12 @@
         <v>1600</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B58" s="3">
         <v>260401</v>
@@ -8089,12 +9059,12 @@
         <v>3200</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B59" s="3">
         <v>260401</v>
@@ -8115,12 +9085,12 @@
         <v>200</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B60" s="3">
         <v>260401</v>
@@ -8141,12 +9111,12 @@
         <v>400</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B61" s="3">
         <v>260401</v>
@@ -8167,12 +9137,12 @@
         <v>800</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B62" s="3">
         <v>260401</v>
@@ -8193,12 +9163,12 @@
         <v>1600</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B63" s="3">
         <v>260401</v>
@@ -8219,12 +9189,12 @@
         <v>3200</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3">
         <v>260401</v>
@@ -8245,12 +9215,12 @@
         <v>200</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B65" s="3">
         <v>260401</v>
@@ -8271,12 +9241,12 @@
         <v>400</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B66" s="3">
         <v>260401</v>
@@ -8297,12 +9267,12 @@
         <v>800</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B67" s="3">
         <v>260401</v>
@@ -8323,12 +9293,12 @@
         <v>1600</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B68" s="3">
         <v>260401</v>
@@ -8349,12 +9319,12 @@
         <v>3200</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B69" s="3">
         <v>260401</v>
@@ -8375,12 +9345,12 @@
         <v>200</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B70" s="3">
         <v>260401</v>
@@ -8401,12 +9371,12 @@
         <v>400</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B71" s="3">
         <v>260401</v>
@@ -8427,12 +9397,12 @@
         <v>800</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B72" s="3">
         <v>260401</v>
@@ -8453,12 +9423,12 @@
         <v>1600</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B73" s="3">
         <v>260401</v>
@@ -8479,12 +9449,12 @@
         <v>3200</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B74" s="3">
         <v>260401</v>
@@ -8505,12 +9475,12 @@
         <v>200</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B75" s="3">
         <v>260401</v>
@@ -8531,12 +9501,12 @@
         <v>400</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B76" s="3">
         <v>260401</v>
@@ -8557,12 +9527,12 @@
         <v>800</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B77" s="3">
         <v>260401</v>
@@ -8583,12 +9553,12 @@
         <v>1600</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B78" s="3">
         <v>260401</v>
@@ -8609,12 +9579,12 @@
         <v>3200</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B79" s="3">
         <v>260401</v>
@@ -8635,12 +9605,12 @@
         <v>200</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B80" s="3">
         <v>260401</v>
@@ -8661,12 +9631,12 @@
         <v>400</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B81" s="3">
         <v>260401</v>
@@ -8687,12 +9657,12 @@
         <v>800</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B82" s="3">
         <v>260401</v>
@@ -8713,12 +9683,12 @@
         <v>1600</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B83" s="3">
         <v>260401</v>
@@ -8739,12 +9709,12 @@
         <v>3200</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B84" s="3">
         <v>260401</v>
@@ -8765,12 +9735,12 @@
         <v>200</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B85" s="3">
         <v>260401</v>
@@ -8791,12 +9761,12 @@
         <v>400</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B86" s="3">
         <v>260401</v>
@@ -8817,12 +9787,12 @@
         <v>800</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B87" s="3">
         <v>260401</v>
@@ -8843,12 +9813,12 @@
         <v>1600</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="88" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B88" s="6">
         <v>260401</v>
@@ -8869,7 +9839,7 @@
         <v>3200</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="Q88" s="3"/>
     </row>
@@ -8893,12 +9863,12 @@
         <v>100</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B90" s="3">
         <v>260401</v>
@@ -8919,12 +9889,12 @@
         <v>200</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B91" s="3">
         <v>260401</v>
@@ -8945,12 +9915,12 @@
         <v>400</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B92" s="3">
         <v>260401</v>
@@ -8971,12 +9941,12 @@
         <v>800</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B93" s="3">
         <v>260401</v>
@@ -8997,12 +9967,12 @@
         <v>1600</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B94" s="3">
         <v>260401</v>
@@ -9023,12 +9993,12 @@
         <v>3200</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B95" s="3">
         <v>260401</v>
@@ -9049,12 +10019,12 @@
         <v>200</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B96" s="3">
         <v>260401</v>
@@ -9075,12 +10045,12 @@
         <v>400</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B97" s="3">
         <v>260401</v>
@@ -9101,12 +10071,12 @@
         <v>800</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B98" s="3">
         <v>260401</v>
@@ -9127,12 +10097,12 @@
         <v>1600</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B99" s="3">
         <v>260401</v>
@@ -9153,12 +10123,12 @@
         <v>3200</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B100" s="3">
         <v>260401</v>
@@ -9179,12 +10149,12 @@
         <v>200</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B101" s="3">
         <v>260401</v>
@@ -9205,12 +10175,12 @@
         <v>400</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B102" s="3">
         <v>260401</v>
@@ -9231,12 +10201,12 @@
         <v>800</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B103" s="3">
         <v>260401</v>
@@ -9257,12 +10227,12 @@
         <v>1600</v>
       </c>
       <c r="P103" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B104" s="3">
         <v>260401</v>
@@ -9283,12 +10253,12 @@
         <v>3200</v>
       </c>
       <c r="P104" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B105" s="3">
         <v>260401</v>
@@ -9309,12 +10279,12 @@
         <v>200</v>
       </c>
       <c r="P105" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B106" s="3">
         <v>260401</v>
@@ -9335,12 +10305,12 @@
         <v>400</v>
       </c>
       <c r="P106" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B107" s="3">
         <v>260401</v>
@@ -9361,12 +10331,12 @@
         <v>800</v>
       </c>
       <c r="P107" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B108" s="3">
         <v>260401</v>
@@ -9387,12 +10357,12 @@
         <v>1600</v>
       </c>
       <c r="P108" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B109" s="3">
         <v>260401</v>
@@ -9413,12 +10383,12 @@
         <v>3200</v>
       </c>
       <c r="P109" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B110" s="3">
         <v>260401</v>
@@ -9439,12 +10409,12 @@
         <v>200</v>
       </c>
       <c r="P110" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B111" s="3">
         <v>260401</v>
@@ -9465,12 +10435,12 @@
         <v>400</v>
       </c>
       <c r="P111" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B112" s="3">
         <v>260401</v>
@@ -9491,12 +10461,12 @@
         <v>800</v>
       </c>
       <c r="P112" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B113" s="3">
         <v>260401</v>
@@ -9517,12 +10487,12 @@
         <v>1600</v>
       </c>
       <c r="P113" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B114" s="3">
         <v>260401</v>
@@ -9543,12 +10513,12 @@
         <v>3200</v>
       </c>
       <c r="P114" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B115" s="3">
         <v>260401</v>
@@ -9569,12 +10539,12 @@
         <v>200</v>
       </c>
       <c r="P115" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B116" s="3">
         <v>260401</v>
@@ -9595,12 +10565,12 @@
         <v>400</v>
       </c>
       <c r="P116" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B117" s="3">
         <v>260401</v>
@@ -9621,12 +10591,12 @@
         <v>800</v>
       </c>
       <c r="P117" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B118" s="3">
         <v>260401</v>
@@ -9647,12 +10617,12 @@
         <v>1600</v>
       </c>
       <c r="P118" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B119" s="3">
         <v>260401</v>
@@ -9673,12 +10643,12 @@
         <v>3200</v>
       </c>
       <c r="P119" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B120" s="3">
         <v>260401</v>
@@ -9699,12 +10669,12 @@
         <v>200</v>
       </c>
       <c r="P120" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B121" s="3">
         <v>260401</v>
@@ -9725,12 +10695,12 @@
         <v>400</v>
       </c>
       <c r="P121" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B122" s="3">
         <v>260401</v>
@@ -9751,12 +10721,12 @@
         <v>800</v>
       </c>
       <c r="P122" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B123" s="3">
         <v>260401</v>
@@ -9777,12 +10747,12 @@
         <v>1600</v>
       </c>
       <c r="P123" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="124" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B124" s="6">
         <v>260401</v>
@@ -9803,7 +10773,7 @@
         <v>3200</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="Q124" s="3"/>
     </row>
@@ -9814,7 +10784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9093C90-CA1C-4140-BA4D-6C6669C599EE}">
   <dimension ref="A1:M88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9843,7 +10813,7 @@
         <v>46</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -9863,7 +10833,7 @@
         <v>99</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
